--- a/invoice_agent/exgrowth_202608.xlsx
+++ b/invoice_agent/exgrowth_202608.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,18 +474,18 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46265</v>
+        <v>46261</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>メール配信サポート6社</t>
+          <t>コンテンツ納品（8/17、8/27×2）</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>60000</v>
+        <v>30000</v>
       </c>
       <c r="F2" t="n">
         <v>10</v>
@@ -496,39 +496,7 @@
         </is>
       </c>
       <c r="H2" s="1" t="n">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Exgrowth株式会社</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>コンテンツ納品</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>業務委託契約</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>46265</v>
+        <v>46261</v>
       </c>
     </row>
   </sheetData>

--- a/invoice_agent/exgrowth_202608.xlsx
+++ b/invoice_agent/exgrowth_202608.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,6 +497,38 @@
       </c>
       <c r="H2" s="1" t="n">
         <v>46261</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Exgrowth株式会社</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>メール配信サポート</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>60000</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>業務委託契約</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>46265</v>
       </c>
     </row>
   </sheetData>

--- a/invoice_agent/exgrowth_202608.xlsx
+++ b/invoice_agent/exgrowth_202608.xlsx
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>30000</v>
+        <v>10000</v>
       </c>
       <c r="F2" t="n">
         <v>10</v>
@@ -496,7 +496,12 @@
         </is>
       </c>
       <c r="H2" s="1" t="n">
-        <v>46261</v>
+        <v>46265</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Facebook広告、各種提案資料の作成等につきましては、メール配信サポートの中で実施させていただきました。</t>
+        </is>
       </c>
     </row>
     <row r="3">
